--- a/SuppXLS/Scen_z_MACC-TRA-CAPs.xlsx
+++ b/SuppXLS/Scen_z_MACC-TRA-CAPs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rbsul\Documents\GitHub\times-ireland-model\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35D72EDE-4871-4B81-91C1-7BC8AD69670E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE14629C-4DC4-4DCC-9516-97910B08AACD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UCT2" sheetId="12" r:id="rId1"/>
@@ -177,9 +177,6 @@
     <t>UC_RHSRT~0</t>
   </si>
   <si>
-    <t>LO</t>
-  </si>
-  <si>
     <t>Coefficient</t>
   </si>
   <si>
@@ -292,6 +289,9 @@
   </si>
   <si>
     <t>T-BUS-FCV*</t>
+  </si>
+  <si>
+    <t>FX</t>
   </si>
 </sst>
 </file>
@@ -951,7 +951,18 @@
     <cellStyle name="Total" xfId="19" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="16" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1252,39 +1263,39 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:AO13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="13" max="13" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.54296875" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>14</v>
       </c>
       <c r="N1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O1">
         <v>0.98</v>
       </c>
     </row>
-    <row r="2" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:41" x14ac:dyDescent="0.35">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:41" x14ac:dyDescent="0.35">
       <c r="B3" s="7" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:41" x14ac:dyDescent="0.35">
       <c r="J4" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.35">
       <c r="B5" s="5" t="s">
         <v>1</v>
       </c>
@@ -1406,7 +1417,7 @@
         <v>2051</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
         <v>33</v>
       </c>
@@ -1414,7 +1425,7 @@
         <v>39</v>
       </c>
       <c r="J6" t="s">
-        <v>47</v>
+        <v>85</v>
       </c>
       <c r="K6">
         <v>1</v>
@@ -1526,7 +1537,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.35">
       <c r="B7" t="s">
         <v>34</v>
       </c>
@@ -1534,7 +1545,7 @@
         <v>40</v>
       </c>
       <c r="J7" t="s">
-        <v>47</v>
+        <v>85</v>
       </c>
       <c r="K7">
         <v>1</v>
@@ -1646,7 +1657,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
         <v>35</v>
       </c>
@@ -1654,7 +1665,7 @@
         <v>41</v>
       </c>
       <c r="J8" t="s">
-        <v>47</v>
+        <v>85</v>
       </c>
       <c r="K8">
         <v>1</v>
@@ -1766,7 +1777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
         <v>36</v>
       </c>
@@ -1774,7 +1785,7 @@
         <v>43</v>
       </c>
       <c r="J9" t="s">
-        <v>47</v>
+        <v>85</v>
       </c>
       <c r="K9">
         <v>1</v>
@@ -1886,7 +1897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
         <v>37</v>
       </c>
@@ -1894,7 +1905,7 @@
         <v>42</v>
       </c>
       <c r="J10" t="s">
-        <v>47</v>
+        <v>85</v>
       </c>
       <c r="K10">
         <v>1</v>
@@ -2006,7 +2017,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
         <v>38</v>
       </c>
@@ -2014,7 +2025,7 @@
         <v>44</v>
       </c>
       <c r="J11" t="s">
-        <v>47</v>
+        <v>85</v>
       </c>
       <c r="K11">
         <v>1</v>
@@ -2126,15 +2137,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.35">
       <c r="B12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D12" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J12" t="s">
-        <v>47</v>
+        <v>85</v>
       </c>
       <c r="K12">
         <v>1</v>
@@ -2246,15 +2257,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.35">
       <c r="B13" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D13" t="s">
+        <v>84</v>
+      </c>
+      <c r="J13" t="s">
         <v>85</v>
-      </c>
-      <c r="J13" t="s">
-        <v>47</v>
       </c>
       <c r="K13">
         <v>1</v>
@@ -2368,6 +2379,12 @@
     </row>
   </sheetData>
   <phoneticPr fontId="23" type="noConversion"/>
+  <conditionalFormatting sqref="P6:AN13">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="between">
+      <formula>0.000000000001</formula>
+      <formula>0.001</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
@@ -2376,13 +2393,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE338A6B-6D9E-4684-8FAB-AE85D1E791FC}">
   <dimension ref="A1:AK73"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="22.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>15</v>
       </c>
@@ -2492,7 +2509,7 @@
         <v>2051</v>
       </c>
     </row>
-    <row r="2" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>17</v>
       </c>
@@ -2603,7 +2620,7 @@
       </c>
       <c r="AK2" s="9"/>
     </row>
-    <row r="3" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -2714,7 +2731,7 @@
       </c>
       <c r="AK3" s="9"/>
     </row>
-    <row r="4" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -2825,7 +2842,7 @@
       </c>
       <c r="AK4" s="9"/>
     </row>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -2936,7 +2953,7 @@
       </c>
       <c r="AK5" s="9"/>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -3047,7 +3064,7 @@
       </c>
       <c r="AK6" s="9"/>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -3158,7 +3175,7 @@
       </c>
       <c r="AK7" s="9"/>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>25</v>
       </c>
@@ -3269,7 +3286,7 @@
       </c>
       <c r="AK8" s="9"/>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>25</v>
       </c>
@@ -3380,7 +3397,7 @@
       </c>
       <c r="AK9" s="9"/>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -3491,7 +3508,7 @@
       </c>
       <c r="AK10" s="9"/>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>28</v>
       </c>
@@ -3602,7 +3619,7 @@
       </c>
       <c r="AK11" s="9"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>28</v>
       </c>
@@ -3713,7 +3730,7 @@
       </c>
       <c r="AK12" s="9"/>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>28</v>
       </c>
@@ -3824,15 +3841,15 @@
       </c>
       <c r="AK13" s="9"/>
     </row>
-    <row r="23" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A23" s="11" t="s">
         <v>9</v>
       </c>
       <c r="B23" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="C23" s="11" t="s">
         <v>49</v>
-      </c>
-      <c r="C23" s="11" t="s">
-        <v>50</v>
       </c>
       <c r="D23" s="12">
         <v>2018</v>
@@ -3937,15 +3954,15 @@
         <v>2051</v>
       </c>
     </row>
-    <row r="24" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A24" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="B24" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="B24" s="13" t="s">
+      <c r="C24" s="13" t="s">
         <v>52</v>
-      </c>
-      <c r="C24" s="13" t="s">
-        <v>53</v>
       </c>
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
@@ -4044,15 +4061,15 @@
         <v>13.4408483244348</v>
       </c>
     </row>
-    <row r="25" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A25" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="B25" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="B25" s="13" t="s">
-        <v>52</v>
-      </c>
       <c r="C25" s="13" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D25" s="14"/>
       <c r="E25" s="14"/>
@@ -4095,15 +4112,15 @@
         <v>6.6598904819665097E-8</v>
       </c>
     </row>
-    <row r="26" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A26" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="B26" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="B26" s="13" t="s">
-        <v>52</v>
-      </c>
       <c r="C26" s="13" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D26" s="14"/>
       <c r="E26" s="15">
@@ -4206,15 +4223,15 @@
         <v>0.73036775892461003</v>
       </c>
     </row>
-    <row r="27" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A27" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="B27" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="B27" s="13" t="s">
-        <v>52</v>
-      </c>
       <c r="C27" s="13" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D27" s="15">
         <v>10.695</v>
@@ -4301,15 +4318,15 @@
       <c r="AJ27" s="14"/>
       <c r="AK27" s="14"/>
     </row>
-    <row r="28" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A28" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="B28" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="B28" s="13" t="s">
-        <v>52</v>
-      </c>
       <c r="C28" s="13" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D28" s="14"/>
       <c r="E28" s="15">
@@ -4378,15 +4395,15 @@
         <v>1.52042140902721E-8</v>
       </c>
     </row>
-    <row r="29" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A29" s="13" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B29" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="C29" s="13" t="s">
         <v>58</v>
-      </c>
-      <c r="C29" s="13" t="s">
-        <v>59</v>
       </c>
       <c r="D29" s="14"/>
       <c r="E29" s="15">
@@ -4489,15 +4506,15 @@
         <v>30.802704540059601</v>
       </c>
     </row>
-    <row r="30" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A30" s="13" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D30" s="14"/>
       <c r="E30" s="15">
@@ -4600,15 +4617,15 @@
         <v>4.2137776007557798E-6</v>
       </c>
     </row>
-    <row r="31" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A31" s="13" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D31" s="14"/>
       <c r="E31" s="15">
@@ -4711,15 +4728,15 @@
         <v>4.1592067038606399E-6</v>
       </c>
     </row>
-    <row r="32" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A32" s="13" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D32" s="14"/>
       <c r="E32" s="14"/>
@@ -4800,15 +4817,15 @@
         <v>2.9366666657609102E-7</v>
       </c>
     </row>
-    <row r="33" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A33" s="13" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D33" s="14"/>
       <c r="E33" s="15">
@@ -4911,15 +4928,15 @@
         <v>1.2349022973980301E-7</v>
       </c>
     </row>
-    <row r="34" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A34" s="13" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C34" s="13" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D34" s="15">
         <v>1.35</v>
@@ -5006,15 +5023,15 @@
       <c r="AJ34" s="14"/>
       <c r="AK34" s="14"/>
     </row>
-    <row r="35" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A35" s="13" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D35" s="14"/>
       <c r="E35" s="15">
@@ -5117,15 +5134,15 @@
         <v>9.0223927579122594E-8</v>
       </c>
     </row>
-    <row r="36" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A36" s="13" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D36" s="14"/>
       <c r="E36" s="15">
@@ -5228,15 +5245,15 @@
         <v>2.1631214541954101E-7</v>
       </c>
     </row>
-    <row r="37" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A37" s="13" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D37" s="14"/>
       <c r="E37" s="14"/>
@@ -5277,15 +5294,15 @@
         <v>3.3714599422336698E-8</v>
       </c>
     </row>
-    <row r="38" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A38" s="13" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B38" s="13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D38" s="15">
         <v>17.463000000000001</v>
@@ -5372,15 +5389,15 @@
       <c r="AJ38" s="14"/>
       <c r="AK38" s="14"/>
     </row>
-    <row r="39" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A39" s="13" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B39" s="13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D39" s="14"/>
       <c r="E39" s="15">
@@ -5483,15 +5500,15 @@
         <v>9.7871650898935796E-8</v>
       </c>
     </row>
-    <row r="40" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A40" s="13" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B40" s="13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C40" s="13" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D40" s="14"/>
       <c r="E40" s="14"/>
@@ -5578,15 +5595,15 @@
         <v>1.29204405934922E-7</v>
       </c>
     </row>
-    <row r="41" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A41" s="13" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B41" s="13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C41" s="13" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D41" s="15">
         <v>2.5</v>
@@ -5673,15 +5690,15 @@
       <c r="AJ41" s="14"/>
       <c r="AK41" s="14"/>
     </row>
-    <row r="42" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A42" s="13" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B42" s="13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D42" s="14"/>
       <c r="E42" s="14"/>
@@ -5724,15 +5741,15 @@
         <v>6.7226475639796806E-8</v>
       </c>
     </row>
-    <row r="43" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A43" s="13" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B43" s="13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D43" s="14"/>
       <c r="E43" s="14"/>
@@ -5809,15 +5826,15 @@
         <v>2.9887533314216802E-7</v>
       </c>
     </row>
-    <row r="44" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A44" s="13" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B44" s="13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C44" s="13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D44" s="14"/>
       <c r="E44" s="14"/>
@@ -5856,15 +5873,15 @@
         <v>1.48687175087375E-8</v>
       </c>
     </row>
-    <row r="45" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A45" s="13" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B45" s="13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C45" s="13" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D45" s="14"/>
       <c r="E45" s="15">
@@ -5967,15 +5984,15 @@
         <v>3.8892186315015997E-6</v>
       </c>
     </row>
-    <row r="46" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A46" s="13" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B46" s="13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C46" s="13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D46" s="14"/>
       <c r="E46" s="15">
@@ -6078,15 +6095,15 @@
         <v>3.8021322144029702E-6</v>
       </c>
     </row>
-    <row r="47" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A47" s="13" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B47" s="13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C47" s="13" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D47" s="14"/>
       <c r="E47" s="15">
@@ -6189,15 +6206,15 @@
         <v>4.0353338430170298E-6</v>
       </c>
     </row>
-    <row r="48" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A48" s="13" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B48" s="13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C48" s="13" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D48" s="14"/>
       <c r="E48" s="15">
@@ -6300,15 +6317,15 @@
         <v>4.3033950169944801E-6</v>
       </c>
     </row>
-    <row r="49" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A49" s="13" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B49" s="13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C49" s="13" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D49" s="14"/>
       <c r="E49" s="15">
@@ -6411,15 +6428,15 @@
         <v>4.04433599321733E-6</v>
       </c>
     </row>
-    <row r="50" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A50" s="13" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B50" s="13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C50" s="13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D50" s="14"/>
       <c r="E50" s="15">
@@ -6522,15 +6539,15 @@
         <v>4.5554380066435304E-6</v>
       </c>
     </row>
-    <row r="51" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A51" s="13" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B51" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="C51" s="13" t="s">
         <v>52</v>
-      </c>
-      <c r="C51" s="13" t="s">
-        <v>53</v>
       </c>
       <c r="D51" s="14"/>
       <c r="E51" s="14"/>
@@ -6601,15 +6618,15 @@
         <v>2.40515383884496</v>
       </c>
     </row>
-    <row r="52" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A52" s="13" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B52" s="13" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C52" s="13" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D52" s="14"/>
       <c r="E52" s="14"/>
@@ -6652,15 +6669,15 @@
         <v>3.1136518546289699E-8</v>
       </c>
     </row>
-    <row r="53" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A53" s="13" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B53" s="13" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C53" s="13" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D53" s="14"/>
       <c r="E53" s="15">
@@ -6715,15 +6732,15 @@
       <c r="AJ53" s="14"/>
       <c r="AK53" s="14"/>
     </row>
-    <row r="54" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A54" s="13" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B54" s="13" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C54" s="13" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D54" s="14"/>
       <c r="E54" s="15">
@@ -6764,15 +6781,15 @@
         <v>1.52042140902721E-8</v>
       </c>
     </row>
-    <row r="55" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A55" s="13" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B55" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="C55" s="13" t="s">
         <v>58</v>
-      </c>
-      <c r="C55" s="13" t="s">
-        <v>59</v>
       </c>
       <c r="D55" s="14"/>
       <c r="E55" s="15">
@@ -6867,15 +6884,15 @@
         <v>0.75713946746556504</v>
       </c>
     </row>
-    <row r="56" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A56" s="13" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B56" s="13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C56" s="13" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D56" s="14"/>
       <c r="E56" s="15">
@@ -6968,15 +6985,15 @@
         <v>4.17814003579881E-7</v>
       </c>
     </row>
-    <row r="57" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A57" s="13" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B57" s="13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C57" s="13" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D57" s="14"/>
       <c r="E57" s="15">
@@ -7067,15 +7084,15 @@
         <v>4.3019784337269199E-7</v>
       </c>
     </row>
-    <row r="58" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A58" s="13" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B58" s="13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C58" s="13" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D58" s="14"/>
       <c r="E58" s="14"/>
@@ -7152,15 +7169,15 @@
         <v>6.2494691447003396E-8</v>
       </c>
     </row>
-    <row r="59" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A59" s="13" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B59" s="13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C59" s="13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D59" s="14"/>
       <c r="E59" s="15">
@@ -7211,15 +7228,15 @@
         <v>5.3641648051865699E-8</v>
       </c>
     </row>
-    <row r="60" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A60" s="13" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B60" s="13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C60" s="13" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D60" s="14"/>
       <c r="E60" s="15">
@@ -7268,15 +7285,15 @@
         <v>4.6650775649426199E-8</v>
       </c>
     </row>
-    <row r="61" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A61" s="13" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B61" s="13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C61" s="13" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D61" s="14"/>
       <c r="E61" s="15">
@@ -7343,15 +7360,15 @@
         <v>5.5067144109155798E-8</v>
       </c>
     </row>
-    <row r="62" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A62" s="13" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B62" s="13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C62" s="13" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D62" s="14"/>
       <c r="E62" s="14"/>
@@ -7392,15 +7409,15 @@
         <v>2.2257851393038599E-8</v>
       </c>
     </row>
-    <row r="63" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A63" s="13" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B63" s="13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C63" s="13" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D63" s="14"/>
       <c r="E63" s="15">
@@ -7451,15 +7468,15 @@
         <v>4.9984491764788603E-8</v>
       </c>
     </row>
-    <row r="64" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A64" s="13" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B64" s="13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C64" s="13" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D64" s="14"/>
       <c r="E64" s="14"/>
@@ -7518,15 +7535,15 @@
         <v>3.8749684299775202E-8</v>
       </c>
     </row>
-    <row r="65" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A65" s="13" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B65" s="13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C65" s="13" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D65" s="14"/>
       <c r="E65" s="14"/>
@@ -7569,15 +7586,15 @@
         <v>4.0371370493911698E-8</v>
       </c>
     </row>
-    <row r="66" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A66" s="13" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B66" s="13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C66" s="13" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D66" s="14"/>
       <c r="E66" s="14"/>
@@ -7654,15 +7671,15 @@
         <v>5.3171913339119603E-8</v>
       </c>
     </row>
-    <row r="67" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A67" s="13" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B67" s="13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C67" s="13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D67" s="14"/>
       <c r="E67" s="14"/>
@@ -7701,15 +7718,15 @@
         <v>1.48687175087375E-8</v>
       </c>
     </row>
-    <row r="68" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A68" s="13" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B68" s="13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C68" s="13" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D68" s="14"/>
       <c r="E68" s="15">
@@ -7800,15 +7817,15 @@
         <v>5.1925826678701999E-7</v>
       </c>
     </row>
-    <row r="69" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A69" s="13" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B69" s="13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C69" s="13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D69" s="14"/>
       <c r="E69" s="15">
@@ -7907,15 +7924,15 @@
         <v>5.4842696740570803E-7</v>
       </c>
     </row>
-    <row r="70" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A70" s="13" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B70" s="13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C70" s="13" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D70" s="14"/>
       <c r="E70" s="15">
@@ -7992,15 +8009,15 @@
         <v>5.2648537289915305E-7</v>
       </c>
     </row>
-    <row r="71" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A71" s="13" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B71" s="13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C71" s="13" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D71" s="14"/>
       <c r="E71" s="15">
@@ -8089,15 +8106,15 @@
         <v>6.1883624539054496E-7</v>
       </c>
     </row>
-    <row r="72" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A72" s="13" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B72" s="13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C72" s="13" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D72" s="14"/>
       <c r="E72" s="15">
@@ -8174,15 +8191,15 @@
         <v>5.2131022058576003E-7</v>
       </c>
     </row>
-    <row r="73" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A73" s="13" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B73" s="13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C73" s="13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D73" s="14"/>
       <c r="E73" s="15">
